--- a/북원_후원업체_지도관리.xlsx
+++ b/북원_후원업체_지도관리.xlsx
@@ -118,7 +118,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -140,6 +140,12 @@
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -636,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H30"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -1572,6 +1578,36 @@
         <v>127.97535913134</v>
       </c>
       <c r="H30" s="10" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>★지오코딩테스트(삭제예정)★</t>
+        </is>
+      </c>
+      <c r="C31" s="12" t="inlineStr">
+        <is>
+          <t>기타</t>
+        </is>
+      </c>
+      <c r="D31" s="11" t="inlineStr">
+        <is>
+          <t>강원 원주시 흥양로50번길 5</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr"/>
+      <c r="F31" s="12" t="inlineStr"/>
+      <c r="G31" s="12" t="inlineStr"/>
+      <c r="H31" s="13" t="inlineStr">
+        <is>
+          <t>자동좌표 테스트</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A4:H30"/>

--- a/북원_후원업체_지도관리.xlsx
+++ b/북원_후원업체_지도관리.xlsx
@@ -642,7 +642,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H31"/>
+  <dimension ref="A1:H30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -712,17 +712,17 @@
       </c>
     </row>
     <row r="5">
-      <c r="A5" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B5" s="10" t="inlineStr">
+      <c r="A5" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>윤가네숯불구이</t>
         </is>
       </c>
-      <c r="C5" s="9" t="inlineStr">
+      <c r="C5" s="12" t="inlineStr">
         <is>
           <t>음식점</t>
         </is>
@@ -732,31 +732,31 @@
           <t>강원 원주시 태장둔치길 23 1층</t>
         </is>
       </c>
-      <c r="E5" s="10" t="inlineStr">
+      <c r="E5" s="13" t="inlineStr">
         <is>
           <t>033-731-2043</t>
         </is>
       </c>
-      <c r="F5" s="9" t="n">
+      <c r="F5" s="12" t="n">
         <v>37.3834800559023</v>
       </c>
-      <c r="G5" s="9" t="n">
+      <c r="G5" s="12" t="n">
         <v>127.95017812945</v>
       </c>
-      <c r="H5" s="10" t="inlineStr"/>
+      <c r="H5" s="13" t="inlineStr"/>
     </row>
     <row r="6">
-      <c r="A6" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B6" s="10" t="inlineStr">
+      <c r="A6" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>태장원마트</t>
         </is>
       </c>
-      <c r="C6" s="9" t="inlineStr">
+      <c r="C6" s="12" t="inlineStr">
         <is>
           <t>마트</t>
         </is>
@@ -766,31 +766,31 @@
           <t>강원 원주시 흥양로51번길 1</t>
         </is>
       </c>
-      <c r="E6" s="10" t="inlineStr">
+      <c r="E6" s="13" t="inlineStr">
         <is>
           <t>033-731-6711</t>
         </is>
       </c>
-      <c r="F6" s="9" t="n">
+      <c r="F6" s="12" t="n">
         <v>37.3839877080173</v>
       </c>
-      <c r="G6" s="9" t="n">
+      <c r="G6" s="12" t="n">
         <v>127.952570458631</v>
       </c>
-      <c r="H6" s="10" t="inlineStr"/>
+      <c r="H6" s="13" t="inlineStr"/>
     </row>
     <row r="7">
-      <c r="A7" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B7" s="10" t="inlineStr">
+      <c r="A7" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>조은가정의원</t>
         </is>
       </c>
-      <c r="C7" s="9" t="inlineStr">
+      <c r="C7" s="12" t="inlineStr">
         <is>
           <t>병원</t>
         </is>
@@ -800,31 +800,31 @@
           <t>강원 원주시 태장둔치길 41</t>
         </is>
       </c>
-      <c r="E7" s="10" t="inlineStr">
+      <c r="E7" s="13" t="inlineStr">
         <is>
           <t>033-745-7734</t>
         </is>
       </c>
-      <c r="F7" s="9" t="n">
+      <c r="F7" s="12" t="n">
         <v>37.3837606112538</v>
       </c>
-      <c r="G7" s="9" t="n">
+      <c r="G7" s="12" t="n">
         <v>127.952028098379</v>
       </c>
-      <c r="H7" s="10" t="inlineStr"/>
+      <c r="H7" s="13" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B8" s="10" t="inlineStr">
+      <c r="A8" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>장상철유명숯불갈비</t>
         </is>
       </c>
-      <c r="C8" s="9" t="inlineStr">
+      <c r="C8" s="12" t="inlineStr">
         <is>
           <t>음식점</t>
         </is>
@@ -834,31 +834,31 @@
           <t>강원 원주시 북원상가길 38</t>
         </is>
       </c>
-      <c r="E8" s="10" t="inlineStr">
+      <c r="E8" s="13" t="inlineStr">
         <is>
           <t>033-734-4321</t>
         </is>
       </c>
-      <c r="F8" s="9" t="n">
+      <c r="F8" s="12" t="n">
         <v>37.3834509740227</v>
       </c>
-      <c r="G8" s="9" t="n">
+      <c r="G8" s="12" t="n">
         <v>127.950691278202</v>
       </c>
-      <c r="H8" s="10" t="inlineStr"/>
+      <c r="H8" s="13" t="inlineStr"/>
     </row>
     <row r="9">
-      <c r="A9" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B9" s="10" t="inlineStr">
+      <c r="A9" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
         <is>
           <t>김남두 비뇨기과의원</t>
         </is>
       </c>
-      <c r="C9" s="9" t="inlineStr">
+      <c r="C9" s="12" t="inlineStr">
         <is>
           <t>병원</t>
         </is>
@@ -868,31 +868,31 @@
           <t>강원 원주시 원일로 114</t>
         </is>
       </c>
-      <c r="E9" s="10" t="inlineStr">
+      <c r="E9" s="13" t="inlineStr">
         <is>
           <t>033-742-0193</t>
         </is>
       </c>
-      <c r="F9" s="9" t="n">
+      <c r="F9" s="12" t="n">
         <v>37.3499877878517</v>
       </c>
-      <c r="G9" s="9" t="n">
+      <c r="G9" s="12" t="n">
         <v>127.94871831418</v>
       </c>
-      <c r="H9" s="10" t="inlineStr"/>
+      <c r="H9" s="13" t="inlineStr"/>
     </row>
     <row r="10">
-      <c r="A10" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B10" s="10" t="inlineStr">
+      <c r="A10" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>대성공업</t>
         </is>
       </c>
-      <c r="C10" s="9" t="inlineStr">
+      <c r="C10" s="12" t="inlineStr">
         <is>
           <t>기업</t>
         </is>
@@ -902,31 +902,31 @@
           <t>강원 원주시 치악로 2078</t>
         </is>
       </c>
-      <c r="E10" s="10" t="inlineStr">
+      <c r="E10" s="13" t="inlineStr">
         <is>
           <t>033-731-4556</t>
         </is>
       </c>
-      <c r="F10" s="9" t="n">
+      <c r="F10" s="12" t="n">
         <v>37.3648569911088</v>
       </c>
-      <c r="G10" s="9" t="n">
+      <c r="G10" s="12" t="n">
         <v>127.962922664209</v>
       </c>
-      <c r="H10" s="10" t="inlineStr"/>
+      <c r="H10" s="13" t="inlineStr"/>
     </row>
     <row r="11">
-      <c r="A11" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B11" s="10" t="inlineStr">
+      <c r="A11" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B11" s="13" t="inlineStr">
         <is>
           <t>서진건설디자인</t>
         </is>
       </c>
-      <c r="C11" s="9" t="inlineStr">
+      <c r="C11" s="12" t="inlineStr">
         <is>
           <t>기업</t>
         </is>
@@ -936,27 +936,27 @@
           <t>강원 원주시 입춘로 45 엔터비즈타워 B동 4층 412, 413호</t>
         </is>
       </c>
-      <c r="E11" s="10" t="inlineStr"/>
-      <c r="F11" s="9" t="n">
+      <c r="E11" s="13" t="inlineStr"/>
+      <c r="F11" s="12" t="n">
         <v>37.32767880959</v>
       </c>
-      <c r="G11" s="9" t="n">
+      <c r="G11" s="12" t="n">
         <v>127.978389908755</v>
       </c>
-      <c r="H11" s="10" t="inlineStr"/>
+      <c r="H11" s="13" t="inlineStr"/>
     </row>
     <row r="12">
-      <c r="A12" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B12" s="10" t="inlineStr">
+      <c r="A12" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B12" s="13" t="inlineStr">
         <is>
           <t>딸부자통신</t>
         </is>
       </c>
-      <c r="C12" s="9" t="inlineStr">
+      <c r="C12" s="12" t="inlineStr">
         <is>
           <t>휴대폰</t>
         </is>
@@ -966,31 +966,31 @@
           <t>강원 원주시 흥양로 4 1층</t>
         </is>
       </c>
-      <c r="E12" s="10" t="inlineStr">
+      <c r="E12" s="13" t="inlineStr">
         <is>
           <t>0507-1354-1011</t>
         </is>
       </c>
-      <c r="F12" s="9" t="n">
+      <c r="F12" s="12" t="n">
         <v>37.3831209594217</v>
       </c>
-      <c r="G12" s="9" t="n">
+      <c r="G12" s="12" t="n">
         <v>127.947602078416</v>
       </c>
-      <c r="H12" s="10" t="inlineStr"/>
+      <c r="H12" s="13" t="inlineStr"/>
     </row>
     <row r="13">
-      <c r="A13" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B13" s="10" t="inlineStr">
+      <c r="A13" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B13" s="13" t="inlineStr">
         <is>
           <t>태장성결교회</t>
         </is>
       </c>
-      <c r="C13" s="9" t="inlineStr">
+      <c r="C13" s="12" t="inlineStr">
         <is>
           <t>교회</t>
         </is>
@@ -1000,31 +1000,31 @@
           <t>강원 원주시 흥양로102번길 4</t>
         </is>
       </c>
-      <c r="E13" s="10" t="inlineStr">
+      <c r="E13" s="13" t="inlineStr">
         <is>
           <t>0507-1352-6762</t>
         </is>
       </c>
-      <c r="F13" s="9" t="n">
+      <c r="F13" s="12" t="n">
         <v>37.3830414479957</v>
       </c>
-      <c r="G13" s="9" t="n">
+      <c r="G13" s="12" t="n">
         <v>127.958262566497</v>
       </c>
-      <c r="H13" s="10" t="inlineStr"/>
+      <c r="H13" s="13" t="inlineStr"/>
     </row>
     <row r="14">
-      <c r="A14" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B14" s="10" t="inlineStr">
+      <c r="A14" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B14" s="13" t="inlineStr">
         <is>
           <t>웅진미트</t>
         </is>
       </c>
-      <c r="C14" s="9" t="inlineStr">
+      <c r="C14" s="12" t="inlineStr">
         <is>
           <t>육류가공</t>
         </is>
@@ -1034,31 +1034,31 @@
           <t>강원 원주시 무상길 45-21</t>
         </is>
       </c>
-      <c r="E14" s="10" t="inlineStr">
+      <c r="E14" s="13" t="inlineStr">
         <is>
           <t>033-743-5692</t>
         </is>
       </c>
-      <c r="F14" s="9" t="n">
+      <c r="F14" s="12" t="n">
         <v>37.3596295170784</v>
       </c>
-      <c r="G14" s="9" t="n">
+      <c r="G14" s="12" t="n">
         <v>127.924068322241</v>
       </c>
-      <c r="H14" s="10" t="inlineStr"/>
+      <c r="H14" s="13" t="inlineStr"/>
     </row>
     <row r="15">
-      <c r="A15" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B15" s="10" t="inlineStr">
+      <c r="A15" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B15" s="13" t="inlineStr">
         <is>
           <t>송정디지털사무기기</t>
         </is>
       </c>
-      <c r="C15" s="9" t="inlineStr">
+      <c r="C15" s="12" t="inlineStr">
         <is>
           <t>사무용기기</t>
         </is>
@@ -1068,31 +1068,31 @@
           <t>판부면 안담길 27-1</t>
         </is>
       </c>
-      <c r="E15" s="10" t="inlineStr">
+      <c r="E15" s="13" t="inlineStr">
         <is>
           <t>033-761-7162</t>
         </is>
       </c>
-      <c r="F15" s="9" t="n">
+      <c r="F15" s="12" t="n">
         <v>37.3182669984943</v>
       </c>
-      <c r="G15" s="9" t="n">
+      <c r="G15" s="12" t="n">
         <v>127.934938387563</v>
       </c>
-      <c r="H15" s="10" t="inlineStr"/>
+      <c r="H15" s="13" t="inlineStr"/>
     </row>
     <row r="16">
-      <c r="A16" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B16" s="10" t="inlineStr">
+      <c r="A16" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B16" s="13" t="inlineStr">
         <is>
           <t>(주)대원스프링</t>
         </is>
       </c>
-      <c r="C16" s="9" t="inlineStr">
+      <c r="C16" s="12" t="inlineStr">
         <is>
           <t>기업</t>
         </is>
@@ -1102,31 +1102,31 @@
           <t>강원 원주시 평원로 112-1</t>
         </is>
       </c>
-      <c r="E16" s="10" t="inlineStr">
+      <c r="E16" s="13" t="inlineStr">
         <is>
           <t>033-740-9200</t>
         </is>
       </c>
-      <c r="F16" s="9" t="n">
+      <c r="F16" s="12" t="n">
         <v>37.3541790598781</v>
       </c>
-      <c r="G16" s="9" t="n">
+      <c r="G16" s="12" t="n">
         <v>127.947872986644</v>
       </c>
-      <c r="H16" s="10" t="inlineStr"/>
+      <c r="H16" s="13" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B17" s="10" t="inlineStr">
+      <c r="A17" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B17" s="13" t="inlineStr">
         <is>
           <t>태장감리교회</t>
         </is>
       </c>
-      <c r="C17" s="9" t="inlineStr">
+      <c r="C17" s="12" t="inlineStr">
         <is>
           <t>교회</t>
         </is>
@@ -1136,31 +1136,31 @@
           <t>강원 원주시 현충로 261</t>
         </is>
       </c>
-      <c r="E17" s="10" t="inlineStr">
+      <c r="E17" s="13" t="inlineStr">
         <is>
           <t>033-733-0601</t>
         </is>
       </c>
-      <c r="F17" s="9" t="n">
+      <c r="F17" s="12" t="n">
         <v>37.3771719540052</v>
       </c>
-      <c r="G17" s="9" t="n">
+      <c r="G17" s="12" t="n">
         <v>127.94932426533</v>
       </c>
-      <c r="H17" s="10" t="inlineStr"/>
+      <c r="H17" s="13" t="inlineStr"/>
     </row>
     <row r="18">
-      <c r="A18" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B18" s="10" t="inlineStr">
+      <c r="A18" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B18" s="13" t="inlineStr">
         <is>
           <t>용전상사</t>
         </is>
       </c>
-      <c r="C18" s="9" t="inlineStr">
+      <c r="C18" s="12" t="inlineStr">
         <is>
           <t>기업</t>
         </is>
@@ -1170,31 +1170,31 @@
           <t>강원 원주시 소초면 진양지길 2</t>
         </is>
       </c>
-      <c r="E18" s="10" t="inlineStr">
+      <c r="E18" s="13" t="inlineStr">
         <is>
           <t>033-742-2879</t>
         </is>
       </c>
-      <c r="F18" s="9" t="n">
+      <c r="F18" s="12" t="n">
         <v>37.3931621674248</v>
       </c>
-      <c r="G18" s="9" t="n">
+      <c r="G18" s="12" t="n">
         <v>127.983490024899</v>
       </c>
-      <c r="H18" s="10" t="inlineStr"/>
+      <c r="H18" s="13" t="inlineStr"/>
     </row>
     <row r="19">
-      <c r="A19" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B19" s="10" t="inlineStr">
+      <c r="A19" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B19" s="13" t="inlineStr">
         <is>
           <t>서진건설디자인(주)</t>
         </is>
       </c>
-      <c r="C19" s="9" t="inlineStr">
+      <c r="C19" s="12" t="inlineStr">
         <is>
           <t>기업</t>
         </is>
@@ -1204,27 +1204,27 @@
           <t>강원 원주시 입춘로 45 엔터비즈타워 B동 4층 412, 413호</t>
         </is>
       </c>
-      <c r="E19" s="10" t="inlineStr"/>
-      <c r="F19" s="9" t="n">
+      <c r="E19" s="13" t="inlineStr"/>
+      <c r="F19" s="12" t="n">
         <v>37.32767880959</v>
       </c>
-      <c r="G19" s="9" t="n">
+      <c r="G19" s="12" t="n">
         <v>127.978389908755</v>
       </c>
-      <c r="H19" s="10" t="inlineStr"/>
+      <c r="H19" s="13" t="inlineStr"/>
     </row>
     <row r="20">
-      <c r="A20" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B20" s="10" t="inlineStr">
+      <c r="A20" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B20" s="13" t="inlineStr">
         <is>
           <t>한국감정평가사협회</t>
         </is>
       </c>
-      <c r="C20" s="9" t="inlineStr">
+      <c r="C20" s="12" t="inlineStr">
         <is>
           <t>협회</t>
         </is>
@@ -1234,27 +1234,27 @@
           <t>서울 서초구 방배로 52</t>
         </is>
       </c>
-      <c r="E20" s="10" t="inlineStr"/>
-      <c r="F20" s="9" t="n">
+      <c r="E20" s="13" t="inlineStr"/>
+      <c r="F20" s="12" t="n">
         <v>37.4793466181359</v>
       </c>
-      <c r="G20" s="9" t="n">
+      <c r="G20" s="12" t="n">
         <v>126.999436064256</v>
       </c>
-      <c r="H20" s="10" t="inlineStr"/>
+      <c r="H20" s="13" t="inlineStr"/>
     </row>
     <row r="21">
-      <c r="A21" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B21" s="10" t="inlineStr">
+      <c r="A21" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B21" s="13" t="inlineStr">
         <is>
           <t>한국주택금융공사 강원서부지사</t>
         </is>
       </c>
-      <c r="C21" s="9" t="inlineStr">
+      <c r="C21" s="12" t="inlineStr">
         <is>
           <t>공사</t>
         </is>
@@ -1264,27 +1264,27 @@
           <t>강원 춘천시 경춘로 2370 한국교직원공제회 강원회관 4층</t>
         </is>
       </c>
-      <c r="E21" s="10" t="inlineStr"/>
-      <c r="F21" s="9" t="n">
+      <c r="E21" s="13" t="inlineStr"/>
+      <c r="F21" s="12" t="n">
         <v>37.8647561810117</v>
       </c>
-      <c r="G21" s="9" t="n">
+      <c r="G21" s="12" t="n">
         <v>127.721042675305</v>
       </c>
-      <c r="H21" s="10" t="inlineStr"/>
+      <c r="H21" s="13" t="inlineStr"/>
     </row>
     <row r="22">
-      <c r="A22" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B22" s="10" t="inlineStr">
+      <c r="A22" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B22" s="13" t="inlineStr">
         <is>
           <t>오일상사</t>
         </is>
       </c>
-      <c r="C22" s="9" t="inlineStr">
+      <c r="C22" s="12" t="inlineStr">
         <is>
           <t>기업</t>
         </is>
@@ -1294,31 +1294,31 @@
           <t>강원 원주시 현충로 304-2</t>
         </is>
       </c>
-      <c r="E22" s="10" t="inlineStr">
+      <c r="E22" s="13" t="inlineStr">
         <is>
           <t>033-747-5134</t>
         </is>
       </c>
-      <c r="F22" s="9" t="n">
+      <c r="F22" s="12" t="n">
         <v>37.3802582458272</v>
       </c>
-      <c r="G22" s="9" t="n">
+      <c r="G22" s="12" t="n">
         <v>127.948646333947</v>
       </c>
-      <c r="H22" s="10" t="inlineStr"/>
+      <c r="H22" s="13" t="inlineStr"/>
     </row>
     <row r="23">
-      <c r="A23" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B23" s="10" t="inlineStr">
+      <c r="A23" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
         <is>
           <t>(주)우진</t>
         </is>
       </c>
-      <c r="C23" s="9" t="inlineStr">
+      <c r="C23" s="12" t="inlineStr">
         <is>
           <t>기업</t>
         </is>
@@ -1328,31 +1328,31 @@
           <t>강원 원주시 태장공단길 50</t>
         </is>
       </c>
-      <c r="E23" s="10" t="inlineStr">
+      <c r="E23" s="13" t="inlineStr">
         <is>
           <t>033-761-4243</t>
         </is>
       </c>
-      <c r="F23" s="9" t="n">
+      <c r="F23" s="12" t="n">
         <v>37.4042680374089</v>
       </c>
-      <c r="G23" s="9" t="n">
+      <c r="G23" s="12" t="n">
         <v>127.945785707146</v>
       </c>
-      <c r="H23" s="10" t="inlineStr"/>
+      <c r="H23" s="13" t="inlineStr"/>
     </row>
     <row r="24">
-      <c r="A24" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B24" s="10" t="inlineStr">
+      <c r="A24" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
         <is>
           <t>강원부품(주)</t>
         </is>
       </c>
-      <c r="C24" s="9" t="inlineStr">
+      <c r="C24" s="12" t="inlineStr">
         <is>
           <t>기업</t>
         </is>
@@ -1362,31 +1362,31 @@
           <t>강원 원주시 현충로 214</t>
         </is>
       </c>
-      <c r="E24" s="10" t="inlineStr">
+      <c r="E24" s="13" t="inlineStr">
         <is>
           <t>033-743-1850</t>
         </is>
       </c>
-      <c r="F24" s="9" t="n">
+      <c r="F24" s="12" t="n">
         <v>37.3728026159565</v>
       </c>
-      <c r="G24" s="9" t="n">
+      <c r="G24" s="12" t="n">
         <v>127.950330853967</v>
       </c>
-      <c r="H24" s="10" t="inlineStr"/>
+      <c r="H24" s="13" t="inlineStr"/>
     </row>
     <row r="25">
-      <c r="A25" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B25" s="10" t="inlineStr">
+      <c r="A25" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B25" s="13" t="inlineStr">
         <is>
           <t>떡빚는마을</t>
         </is>
       </c>
-      <c r="C25" s="9" t="inlineStr">
+      <c r="C25" s="12" t="inlineStr">
         <is>
           <t>떡</t>
         </is>
@@ -1396,31 +1396,31 @@
           <t>강원 원주시 흥양로 62</t>
         </is>
       </c>
-      <c r="E25" s="10" t="inlineStr">
+      <c r="E25" s="13" t="inlineStr">
         <is>
           <t>033-900-7004</t>
         </is>
       </c>
-      <c r="F25" s="9" t="n">
+      <c r="F25" s="12" t="n">
         <v>37.3830659998128</v>
       </c>
-      <c r="G25" s="9" t="n">
+      <c r="G25" s="12" t="n">
         <v>127.954257184894</v>
       </c>
-      <c r="H25" s="10" t="inlineStr"/>
+      <c r="H25" s="13" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B26" s="10" t="inlineStr">
+      <c r="A26" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B26" s="13" t="inlineStr">
         <is>
           <t>한국광해광업공단</t>
         </is>
       </c>
-      <c r="C26" s="9" t="inlineStr">
+      <c r="C26" s="12" t="inlineStr">
         <is>
           <t>공단</t>
         </is>
@@ -1430,31 +1430,31 @@
           <t>강원 원주시 혁신로 199</t>
         </is>
       </c>
-      <c r="E26" s="10" t="inlineStr">
+      <c r="E26" s="13" t="inlineStr">
         <is>
           <t>033-736-5254</t>
         </is>
       </c>
-      <c r="F26" s="9" t="n">
+      <c r="F26" s="12" t="n">
         <v>37.3256602608297</v>
       </c>
-      <c r="G26" s="9" t="n">
+      <c r="G26" s="12" t="n">
         <v>127.991716831249</v>
       </c>
-      <c r="H26" s="10" t="inlineStr"/>
+      <c r="H26" s="13" t="inlineStr"/>
     </row>
     <row r="27">
-      <c r="A27" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B27" s="10" t="inlineStr">
+      <c r="A27" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B27" s="13" t="inlineStr">
         <is>
           <t>밥상공동체 연탄은행</t>
         </is>
       </c>
-      <c r="C27" s="9" t="inlineStr">
+      <c r="C27" s="12" t="inlineStr">
         <is>
           <t>복지재단</t>
         </is>
@@ -1464,31 +1464,31 @@
           <t>강원 원주시 평원로 6</t>
         </is>
       </c>
-      <c r="E27" s="10" t="inlineStr">
+      <c r="E27" s="13" t="inlineStr">
         <is>
           <t>1577-9044</t>
         </is>
       </c>
-      <c r="F27" s="9" t="n">
+      <c r="F27" s="12" t="n">
         <v>37.3480063267531</v>
       </c>
-      <c r="G27" s="9" t="n">
+      <c r="G27" s="12" t="n">
         <v>127.954004773908</v>
       </c>
-      <c r="H27" s="10" t="inlineStr"/>
+      <c r="H27" s="13" t="inlineStr"/>
     </row>
     <row r="28">
-      <c r="A28" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B28" s="10" t="inlineStr">
+      <c r="A28" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B28" s="13" t="inlineStr">
         <is>
           <t>청산광고</t>
         </is>
       </c>
-      <c r="C28" s="9" t="inlineStr">
+      <c r="C28" s="12" t="inlineStr">
         <is>
           <t>광고</t>
         </is>
@@ -1498,31 +1498,31 @@
           <t>강원 원주시 샘둔지길 10</t>
         </is>
       </c>
-      <c r="E28" s="10" t="inlineStr">
+      <c r="E28" s="13" t="inlineStr">
         <is>
           <t>033-763-4400</t>
         </is>
       </c>
-      <c r="F28" s="9" t="n">
+      <c r="F28" s="12" t="n">
         <v>37.3468267992581</v>
       </c>
-      <c r="G28" s="9" t="n">
+      <c r="G28" s="12" t="n">
         <v>127.935997538842</v>
       </c>
-      <c r="H28" s="10" t="inlineStr"/>
+      <c r="H28" s="13" t="inlineStr"/>
     </row>
     <row r="29">
-      <c r="A29" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B29" s="10" t="inlineStr">
+      <c r="A29" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B29" s="13" t="inlineStr">
         <is>
           <t>나래프린트</t>
         </is>
       </c>
-      <c r="C29" s="9" t="inlineStr">
+      <c r="C29" s="12" t="inlineStr">
         <is>
           <t>광고</t>
         </is>
@@ -1532,31 +1532,31 @@
           <t>강원 원주시 봉화로 173</t>
         </is>
       </c>
-      <c r="E29" s="10" t="inlineStr">
+      <c r="E29" s="13" t="inlineStr">
         <is>
           <t>033-746-0852</t>
         </is>
       </c>
-      <c r="F29" s="9" t="n">
+      <c r="F29" s="12" t="n">
         <v>37.3600411433857</v>
       </c>
-      <c r="G29" s="9" t="n">
+      <c r="G29" s="12" t="n">
         <v>127.929007489512</v>
       </c>
-      <c r="H29" s="10" t="inlineStr"/>
+      <c r="H29" s="13" t="inlineStr"/>
     </row>
     <row r="30">
-      <c r="A30" s="9" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B30" s="10" t="inlineStr">
+      <c r="A30" s="12" t="inlineStr">
+        <is>
+          <t>O</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
         <is>
           <t>한국도로교통공단</t>
         </is>
       </c>
-      <c r="C30" s="9" t="inlineStr">
+      <c r="C30" s="12" t="inlineStr">
         <is>
           <t>공단</t>
         </is>
@@ -1566,48 +1566,18 @@
           <t>강원특별자치도 원주시 혁신로 2 한국도로교통공단 본부</t>
         </is>
       </c>
-      <c r="E30" s="10" t="inlineStr">
+      <c r="E30" s="13" t="inlineStr">
         <is>
           <t>1577-1120</t>
         </is>
       </c>
-      <c r="F30" s="9" t="n">
+      <c r="F30" s="12" t="n">
         <v>37.3244992551977</v>
       </c>
-      <c r="G30" s="9" t="n">
+      <c r="G30" s="12" t="n">
         <v>127.97535913134</v>
       </c>
-      <c r="H30" s="10" t="inlineStr"/>
-    </row>
-    <row r="31">
-      <c r="A31" s="12" t="inlineStr">
-        <is>
-          <t>O</t>
-        </is>
-      </c>
-      <c r="B31" s="13" t="inlineStr">
-        <is>
-          <t>★지오코딩테스트(삭제예정)★</t>
-        </is>
-      </c>
-      <c r="C31" s="12" t="inlineStr">
-        <is>
-          <t>기타</t>
-        </is>
-      </c>
-      <c r="D31" s="11" t="inlineStr">
-        <is>
-          <t>강원 원주시 흥양로50번길 5</t>
-        </is>
-      </c>
-      <c r="E31" s="13" t="inlineStr"/>
-      <c r="F31" s="12" t="inlineStr"/>
-      <c r="G31" s="12" t="inlineStr"/>
-      <c r="H31" s="13" t="inlineStr">
-        <is>
-          <t>자동좌표 테스트</t>
-        </is>
-      </c>
+      <c r="H30" s="13" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:H30"/>
